--- a/outputs/daily/hr_rankings_2026-08-22.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22.xlsx
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -15978,7 +15978,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -16606,7 +16606,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -20120,7 +20120,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -22022,7 +22022,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -22960,7 +22960,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -26100,7 +26100,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -28026,7 +28026,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -29596,7 +29596,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -29910,7 +29910,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -30224,7 +30224,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -36514,7 +36514,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -38084,7 +38084,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -38398,7 +38398,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -40254,7 +40254,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -41842,7 +41842,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -42156,7 +42156,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -43098,7 +43098,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -44082,7 +44082,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -45314,7 +45314,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -47550,7 +47550,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -47864,7 +47864,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -49720,7 +49720,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -50034,7 +50034,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -51604,7 +51604,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -51918,7 +51918,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -53530,7 +53530,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -56042,7 +56042,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -56670,7 +56670,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -56984,7 +56984,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -57926,7 +57926,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -59182,7 +59182,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -59496,7 +59496,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -59810,7 +59810,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -61694,7 +61694,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -63984,7 +63984,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -64926,7 +64926,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -68104,7 +68104,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -68418,7 +68418,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -68732,7 +68732,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-22.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -17566,7 +17566,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -18508,7 +18508,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -19178,7 +19178,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -19492,7 +19492,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -19806,7 +19806,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -21418,7 +21418,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -24844,7 +24844,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -25472,7 +25472,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -25786,7 +25786,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -27712,7 +27712,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -28340,7 +28340,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -31836,7 +31836,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -32126,7 +32126,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -33374,7 +33374,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -34002,7 +34002,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -34316,7 +34316,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -35572,7 +35572,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -35886,7 +35886,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -37456,7 +37456,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -37770,7 +37770,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -38712,7 +38712,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -39336,7 +39336,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -39650,7 +39650,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -39940,7 +39940,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -40924,7 +40924,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -41214,7 +41214,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -41528,7 +41528,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -42470,7 +42470,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -42784,7 +42784,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -43412,7 +43412,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -43726,7 +43726,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -44396,7 +44396,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -44710,7 +44710,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -45628,7 +45628,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -46566,7 +46566,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -48488,7 +48488,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -49092,7 +49092,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -49406,7 +49406,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -50348,7 +50348,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -50662,7 +50662,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -52232,7 +52232,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -52588,7 +52588,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -53216,7 +53216,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -53844,7 +53844,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -54158,7 +54158,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -55100,7 +55100,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -55414,7 +55414,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -55728,7 +55728,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -57298,7 +57298,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -57612,7 +57612,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -58240,7 +58240,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -58554,7 +58554,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -60124,7 +60124,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -60438,7 +60438,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -61066,7 +61066,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -61380,7 +61380,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -62008,7 +62008,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -62322,7 +62322,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -62636,7 +62636,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -62950,7 +62950,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -63670,7 +63670,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -64298,7 +64298,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -64612,7 +64612,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -65240,7 +65240,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -65596,7 +65596,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -65910,7 +65910,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -66534,7 +66534,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -67162,7 +67162,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -67476,7 +67476,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -67790,7 +67790,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -69046,7 +69046,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -69336,7 +69336,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-22.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -15960,7 +15960,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21064,7 +21064,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21378,7 +21378,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22990,7 +22990,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23618,7 +23618,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
